--- a/demo/1_請求_2026年8月（下書き）（前回）.xlsx
+++ b/demo/1_請求_2026年8月（下書き）（前回）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t xml:space="preserve">取引先</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t xml:space="preserve">丸山工業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCパーツ</t>
   </si>
   <si>
     <t xml:space="preserve">みどり建設</t>
@@ -1256,7 +1259,9 @@
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1265,10 +1270,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>9</v>
@@ -1310,7 +1315,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1318,34 +1323,34 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1353,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>3</v>
@@ -1364,24 +1369,24 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1389,15 +1394,15 @@
         <v>6</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1427,80 +1432,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
